--- a/project/output/lulu_valuation_model.xlsx
+++ b/project/output/lulu_valuation_model.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario summary" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sens WACC g" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sens Growth Margin" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market breakeven" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market implied stress" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market implied stress" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market breakeven" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Temporary input: MarketWatch reported LULU closed at $116.21 on 2026-06-15.</t>
+          <t>MarketWatch reported LULU closed at $116.21 on 2026-06-15.</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Temporary input: MarketWatch reported LULU closed at $116.21 on 2026-06-15.</t>
+          <t>MarketWatch reported LULU closed at $116.21 on 2026-06-15.</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Temporary input: MarketWatch reported LULU closed at $116.21 on 2026-06-15.</t>
+          <t>MarketWatch reported LULU closed at $116.21 on 2026-06-15.</t>
         </is>
       </c>
     </row>
@@ -4031,86 +4031,3679 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:I126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>wacc_terminal</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>market_price</t>
+          <t>terminal_growth</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>closest_fair_value_per_share</t>
+          <t>target_operating_margin</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>terminal_wacc</t>
+          <t>year1_growth</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>terminal_growth</t>
+          <t>year5_growth</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>year5_revenue_growth</t>
+          <t>year10_growth</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>target_operating_margin</t>
+          <t>sales_to_capital</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>fair_value_per_share</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>distance_to_market_price</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>terminal_wacc_vs_terminal_growth</t>
-        </is>
+      <c r="A2" t="n">
+        <v>0.12</v>
       </c>
       <c r="B2" t="n">
-        <v>116.21</v>
+        <v>0.02</v>
       </c>
       <c r="C2" t="n">
-        <v>186.6867993212859</v>
+        <v>0.18</v>
       </c>
       <c r="D2" t="n">
-        <v>0.095</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H2" t="n">
+        <v>115.9299487415207</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-0.2800512584792898</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H3" t="n">
+        <v>116.7117790679556</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.5017790679556242</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H4" t="n">
+        <v>116.7576095230824</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.5476095230823717</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H5" t="n">
+        <v>115.4982262411372</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.711773758862833</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>115.3971024418079</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0.8128975581921196</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="B7" t="n">
         <v>0.01</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>year5_growth_vs_target_margin</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>116.21</v>
-      </c>
-      <c r="C3" t="n">
-        <v>185.5451890360578</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="C7" t="n">
         <v>0.17</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H7" t="n">
+        <v>117.7717877553772</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.561787755377196</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H8" t="n">
+        <v>117.8880387307535</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.678038730753499</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H9" t="n">
+        <v>118.0136508076582</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.803650807658173</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H10" t="n">
+        <v>114.3751560283854</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-1.834843971614617</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H11" t="n">
+        <v>113.9659445120454</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-2.244055487954569</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H12" t="n">
+        <v>113.7000320917072</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-2.509967908292779</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H13" t="n">
+        <v>113.4313521372826</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-2.778647862717406</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H14" t="n">
+        <v>113.0422089125426</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-3.167791087457388</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H15" t="n">
+        <v>119.4047800727457</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.194780072745672</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H16" t="n">
+        <v>119.4522862897727</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.242286289772679</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H17" t="n">
+        <v>112.9505369933791</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-3.259463006620905</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H18" t="n">
+        <v>119.8008429433546</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.590842943354573</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H19" t="n">
+        <v>120.0848615247812</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.874861524781238</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H20" t="n">
+        <v>120.2846715342741</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.07467153427406</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H21" t="n">
+        <v>120.5407446857358</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.330744685735851</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>111.6728351373313</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-4.537164862668675</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H23" t="n">
+        <v>111.5198341273205</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-4.690165872679501</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H24" t="n">
+        <v>111.5091451725468</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-4.700854827453185</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>110.9115909574931</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-5.298409042506918</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H26" t="n">
+        <v>110.5095333493417</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-5.700466650658313</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B27" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H27" t="n">
+        <v>122.0060738736179</v>
+      </c>
+      <c r="I27" t="n">
+        <v>5.796073873617928</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B28" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>122.3633824517811</v>
+      </c>
+      <c r="I28" t="n">
+        <v>6.153382451781141</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H29" t="n">
+        <v>122.5013665982118</v>
+      </c>
+      <c r="I29" t="n">
+        <v>6.291366598211766</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H30" t="n">
+        <v>109.8219161789881</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-6.388083821011904</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="B31" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H31" t="n">
+        <v>109.4218237690051</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-6.788176230994935</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H32" t="n">
+        <v>123.0767646219372</v>
+      </c>
+      <c r="I32" t="n">
+        <v>6.86676462193725</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H33" t="n">
+        <v>109.2980257669981</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-6.911974233001899</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H34" t="n">
+        <v>108.9746655438117</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-7.235334456188312</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="B35" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H35" t="n">
+        <v>123.5206879232791</v>
+      </c>
+      <c r="I35" t="n">
+        <v>7.310687923279062</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="B36" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H36" t="n">
+        <v>108.312630069708</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-7.897369930292001</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H37" t="n">
+        <v>108.1252404671735</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-8.084759532826482</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H38" t="n">
+        <v>124.52941655116</v>
+      </c>
+      <c r="I38" t="n">
+        <v>8.319416551160003</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="B39" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H39" t="n">
+        <v>107.8874231791001</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-8.32257682089994</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H40" t="n">
+        <v>124.843615633446</v>
+      </c>
+      <c r="I40" t="n">
+        <v>8.633615633445984</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="B41" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H41" t="n">
+        <v>107.514541625082</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-8.695458374918033</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="B42" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H42" t="n">
+        <v>125.1722406267402</v>
+      </c>
+      <c r="I42" t="n">
+        <v>8.962240626740225</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="B43" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H43" t="n">
+        <v>107.1097195131203</v>
+      </c>
+      <c r="I43" t="n">
+        <v>-9.100280486879711</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B44" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H44" t="n">
+        <v>125.6918101281961</v>
+      </c>
+      <c r="I44" t="n">
+        <v>9.481810128196059</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="B45" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H45" t="n">
+        <v>106.3249556738489</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-9.885044326151046</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="B46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H46" t="n">
+        <v>126.3888768580618</v>
+      </c>
+      <c r="I46" t="n">
+        <v>10.17887685806183</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="B47" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H47" t="n">
+        <v>105.9144593201816</v>
+      </c>
+      <c r="I47" t="n">
+        <v>-10.29554067981842</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="B48" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H48" t="n">
+        <v>105.7731101023696</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-10.43688989763044</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="B49" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H49" t="n">
+        <v>105.6219642568755</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-10.58803574312448</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="B50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H50" t="n">
+        <v>126.8731240655152</v>
+      </c>
+      <c r="I50" t="n">
+        <v>10.66312406551519</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B51" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H51" t="n">
+        <v>127.2545382241535</v>
+      </c>
+      <c r="I51" t="n">
+        <v>11.0445382241535</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="B52" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H52" t="n">
+        <v>105.1436154463029</v>
+      </c>
+      <c r="I52" t="n">
+        <v>-11.06638455369708</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="B53" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H53" t="n">
+        <v>104.5179789503407</v>
+      </c>
+      <c r="I53" t="n">
+        <v>-11.69202104965925</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B54" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H54" t="n">
+        <v>128.0149858356067</v>
+      </c>
+      <c r="I54" t="n">
+        <v>11.80498583560673</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="B55" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H55" t="n">
+        <v>128.1398784362163</v>
+      </c>
+      <c r="I55" t="n">
+        <v>11.9298784362163</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="B56" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H56" t="n">
+        <v>104.2052424471025</v>
+      </c>
+      <c r="I56" t="n">
+        <v>-12.00475755289746</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="B57" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H57" t="n">
+        <v>104.1767978732165</v>
+      </c>
+      <c r="I57" t="n">
+        <v>-12.03320212678348</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="B58" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H58" t="n">
+        <v>103.5830512268734</v>
+      </c>
+      <c r="I58" t="n">
+        <v>-12.62694877312656</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="B59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H59" t="n">
+        <v>103.3562481128326</v>
+      </c>
+      <c r="I59" t="n">
+        <v>-12.85375188716739</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="B60" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H60" t="n">
+        <v>129.5997284124679</v>
+      </c>
+      <c r="I60" t="n">
+        <v>13.38972841246787</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H61" t="n">
+        <v>129.6065468125473</v>
+      </c>
+      <c r="I61" t="n">
+        <v>13.39654681254727</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="B62" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H62" t="n">
+        <v>102.6996048989201</v>
+      </c>
+      <c r="I62" t="n">
+        <v>-13.51039510107992</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="B63" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H63" t="n">
+        <v>102.6384603134468</v>
+      </c>
+      <c r="I63" t="n">
+        <v>-13.57153968655324</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B64" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H64" t="n">
+        <v>130.2824511941463</v>
+      </c>
+      <c r="I64" t="n">
+        <v>14.07245119414627</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="B65" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G65" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H65" t="n">
+        <v>102.0308017948742</v>
+      </c>
+      <c r="I65" t="n">
+        <v>-14.17919820512584</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="B66" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H66" t="n">
+        <v>130.6725516933828</v>
+      </c>
+      <c r="I66" t="n">
+        <v>14.46255169338276</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="B67" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H67" t="n">
+        <v>101.7383203902049</v>
+      </c>
+      <c r="I67" t="n">
+        <v>-14.47167960979509</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="B68" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H68" t="n">
+        <v>101.724304025751</v>
+      </c>
+      <c r="I68" t="n">
+        <v>-14.485695974249</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="B69" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H69" t="n">
+        <v>101.1970207504834</v>
+      </c>
+      <c r="I69" t="n">
+        <v>-15.01297924951656</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="B70" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H70" t="n">
+        <v>100.8654071236008</v>
+      </c>
+      <c r="I70" t="n">
+        <v>-15.34459287639922</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B71" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H71" t="n">
+        <v>131.5827773130376</v>
+      </c>
+      <c r="I71" t="n">
+        <v>15.37277731303756</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="B72" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H72" t="n">
+        <v>100.4226902519484</v>
+      </c>
+      <c r="I72" t="n">
+        <v>-15.78730974805157</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="B73" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H73" t="n">
+        <v>100.2283552792595</v>
+      </c>
+      <c r="I73" t="n">
+        <v>-15.98164472074048</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="B74" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H74" t="n">
+        <v>132.2370090303878</v>
+      </c>
+      <c r="I74" t="n">
+        <v>16.02700903038782</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="B75" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H75" t="n">
+        <v>100.0612923568699</v>
+      </c>
+      <c r="I75" t="n">
+        <v>-16.14870764313014</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B76" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G76" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H76" t="n">
+        <v>132.503002574689</v>
+      </c>
+      <c r="I76" t="n">
+        <v>16.29300257468903</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="B77" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H77" t="n">
+        <v>99.86646115390191</v>
+      </c>
+      <c r="I77" t="n">
+        <v>-16.34353884609808</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="B78" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G78" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H78" t="n">
+        <v>133.2119364111746</v>
+      </c>
+      <c r="I78" t="n">
+        <v>17.00193641117464</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="B79" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H79" t="n">
+        <v>99.19795460058323</v>
+      </c>
+      <c r="I79" t="n">
+        <v>-17.01204539941676</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="B80" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G80" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H80" t="n">
+        <v>98.94858800426653</v>
+      </c>
+      <c r="I80" t="n">
+        <v>-17.26141199573347</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B81" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H81" t="n">
+        <v>133.6665892194323</v>
+      </c>
+      <c r="I81" t="n">
+        <v>17.4565892194323</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="B82" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H82" t="n">
+        <v>98.28949028471988</v>
+      </c>
+      <c r="I82" t="n">
+        <v>-17.92050971528012</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="B83" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G83" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H83" t="n">
+        <v>98.14714426956671</v>
+      </c>
+      <c r="I83" t="n">
+        <v>-18.06285573043328</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="B84" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H84" t="n">
+        <v>97.67549794913243</v>
+      </c>
+      <c r="I84" t="n">
+        <v>-18.53450205086756</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="B85" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H85" t="n">
+        <v>97.59241393639917</v>
+      </c>
+      <c r="I85" t="n">
+        <v>-18.61758606360083</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="B86" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H86" t="n">
+        <v>135.01475469666</v>
+      </c>
+      <c r="I86" t="n">
+        <v>18.80475469666003</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="B87" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H87" t="n">
+        <v>135.6787689016566</v>
+      </c>
+      <c r="I87" t="n">
+        <v>19.46876890165662</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B88" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G88" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H88" t="n">
+        <v>135.7212867548465</v>
+      </c>
+      <c r="I88" t="n">
+        <v>19.51128675484652</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="B89" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H89" t="n">
+        <v>96.64013805679431</v>
+      </c>
+      <c r="I89" t="n">
+        <v>-19.56986194320568</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="B90" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H90" t="n">
+        <v>96.58719880089865</v>
+      </c>
+      <c r="I90" t="n">
+        <v>-19.62280119910135</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="B91" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H91" t="n">
+        <v>96.34056095067547</v>
+      </c>
+      <c r="I91" t="n">
+        <v>-19.86943904932453</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="B92" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G92" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H92" t="n">
+        <v>96.27991268530255</v>
+      </c>
+      <c r="I92" t="n">
+        <v>-19.93008731469745</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="B93" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H93" t="n">
+        <v>95.25871569508628</v>
+      </c>
+      <c r="I93" t="n">
+        <v>-20.95128430491371</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="B94" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H94" t="n">
+        <v>137.3057721430423</v>
+      </c>
+      <c r="I94" t="n">
+        <v>21.09577214304231</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="B95" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H95" t="n">
+        <v>95.0396610883339</v>
+      </c>
+      <c r="I95" t="n">
+        <v>-21.17033891166609</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B96" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G96" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H96" t="n">
+        <v>137.4737444978791</v>
+      </c>
+      <c r="I96" t="n">
+        <v>21.26374449787907</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="B97" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G97" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H97" t="n">
+        <v>138.0851412027138</v>
+      </c>
+      <c r="I97" t="n">
+        <v>21.87514120271381</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="B98" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G98" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H98" t="n">
+        <v>94.26348674425928</v>
+      </c>
+      <c r="I98" t="n">
+        <v>-21.94651325574071</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="B99" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G99" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H99" t="n">
+        <v>93.98780712231489</v>
+      </c>
+      <c r="I99" t="n">
+        <v>-22.2221928776851</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="B100" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G100" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H100" t="n">
+        <v>93.62669187251389</v>
+      </c>
+      <c r="I100" t="n">
+        <v>-22.58330812748611</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B101" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G101" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H101" t="n">
+        <v>139.3181926032578</v>
+      </c>
+      <c r="I101" t="n">
+        <v>23.10819260325782</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="B102" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G102" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H102" t="n">
+        <v>139.5507487568341</v>
+      </c>
+      <c r="I102" t="n">
+        <v>23.34074875683409</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="B103" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G103" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H103" t="n">
+        <v>92.8575858616402</v>
+      </c>
+      <c r="I103" t="n">
+        <v>-23.35241413835979</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="B104" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G104" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H104" t="n">
+        <v>92.814660747449</v>
+      </c>
+      <c r="I104" t="n">
+        <v>-23.395339252551</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="B105" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G105" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H105" t="n">
+        <v>92.33147009134557</v>
+      </c>
+      <c r="I105" t="n">
+        <v>-23.87852990865443</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="B106" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G106" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H106" t="n">
+        <v>91.56884338590604</v>
+      </c>
+      <c r="I106" t="n">
+        <v>-24.64115661409396</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="B107" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G107" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H107" t="n">
+        <v>141.7578093908455</v>
+      </c>
+      <c r="I107" t="n">
+        <v>25.54780939084547</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="B108" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G108" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H108" t="n">
+        <v>141.9844415508911</v>
+      </c>
+      <c r="I108" t="n">
+        <v>25.7744415508911</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="B109" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G109" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H109" t="n">
+        <v>90.38320030823063</v>
+      </c>
+      <c r="I109" t="n">
+        <v>-25.82679969176937</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="B110" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G110" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H110" t="n">
+        <v>90.37982921895185</v>
+      </c>
+      <c r="I110" t="n">
+        <v>-25.83017078104814</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="B111" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G111" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H111" t="n">
+        <v>89.28876054422253</v>
+      </c>
+      <c r="I111" t="n">
+        <v>-26.92123945577747</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="B112" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G112" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H112" t="n">
+        <v>89.07503366648609</v>
+      </c>
+      <c r="I112" t="n">
+        <v>-27.1349663335139</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B113" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G113" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H113" t="n">
+        <v>143.3647116827206</v>
+      </c>
+      <c r="I113" t="n">
+        <v>27.15471168272056</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="B114" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G114" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H114" t="n">
+        <v>143.9332733750397</v>
+      </c>
+      <c r="I114" t="n">
+        <v>27.72327337503974</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="B115" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G115" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H115" t="n">
+        <v>143.9389925927019</v>
+      </c>
+      <c r="I115" t="n">
+        <v>27.72899259270186</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="B116" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G116" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H116" t="n">
+        <v>87.87897107672582</v>
+      </c>
+      <c r="I116" t="n">
+        <v>-28.33102892327418</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H117" t="n">
+        <v>86.77859349414634</v>
+      </c>
+      <c r="I117" t="n">
+        <v>-29.43140650585366</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H118" t="n">
+        <v>145.8895611024936</v>
+      </c>
+      <c r="I118" t="n">
+        <v>29.67956110249357</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H119" t="n">
+        <v>85.76286034099607</v>
+      </c>
+      <c r="I119" t="n">
+        <v>-30.44713965900392</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H120" t="n">
+        <v>147.8368498800342</v>
+      </c>
+      <c r="I120" t="n">
+        <v>31.62684988003424</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H121" t="n">
+        <v>148.9541284051222</v>
+      </c>
+      <c r="I121" t="n">
+        <v>32.74412840512217</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G122" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H122" t="n">
+        <v>150.5722130423615</v>
+      </c>
+      <c r="I122" t="n">
+        <v>34.36221304236146</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H123" t="n">
+        <v>152.228373448153</v>
+      </c>
+      <c r="I123" t="n">
+        <v>36.01837344815301</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C124" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H124" t="n">
+        <v>155.9238152593533</v>
+      </c>
+      <c r="I124" t="n">
+        <v>39.71381525935327</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H125" t="n">
+        <v>157.2054334920209</v>
+      </c>
+      <c r="I125" t="n">
+        <v>40.99543349202095</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H126" t="n">
+        <v>162.8935021135843</v>
+      </c>
+      <c r="I126" t="n">
+        <v>46.68350211358434</v>
       </c>
     </row>
   </sheetData>
@@ -4124,3679 +7717,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I126"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>wacc_terminal</t>
+          <t>table</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>market_price</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>closest_fair_value_per_share</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>terminal_wacc</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>terminal_growth</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>year5_revenue_growth</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>target_operating_margin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>year1_growth</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>year5_growth</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>year10_growth</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>sales_to_capital</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>fair_value_per_share</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>distance_to_market_price</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>0.12</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>terminal_wacc_vs_terminal_growth</t>
+        </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02</v>
+        <v>116.21</v>
       </c>
       <c r="C2" t="n">
-        <v>0.18</v>
+        <v>186.6867993212859</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.095</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H2" t="n">
-        <v>115.9299487415207</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-0.2800512584792898</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>0.1</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>year5_growth_vs_target_margin</t>
+        </is>
       </c>
       <c r="B3" t="n">
-        <v>0.015</v>
+        <v>116.21</v>
       </c>
       <c r="C3" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.02</v>
-      </c>
+        <v>185.5451890360578</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>0.015</v>
+        <v>0.025</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H3" t="n">
-        <v>116.7117790679556</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.5017790679556242</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H4" t="n">
-        <v>116.7576095230824</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.5476095230823717</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C5" t="n">
         <v>0.17</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H5" t="n">
-        <v>115.4982262411372</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-0.711773758862833</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="B6" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H6" t="n">
-        <v>115.3971024418079</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-0.8128975581921196</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H7" t="n">
-        <v>117.7717877553772</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.561787755377196</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H8" t="n">
-        <v>117.8880387307535</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.678038730753499</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H9" t="n">
-        <v>118.0136508076582</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.803650807658173</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H10" t="n">
-        <v>114.3751560283854</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-1.834843971614617</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H11" t="n">
-        <v>113.9659445120454</v>
-      </c>
-      <c r="I11" t="n">
-        <v>-2.244055487954569</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H12" t="n">
-        <v>113.7000320917072</v>
-      </c>
-      <c r="I12" t="n">
-        <v>-2.509967908292779</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H13" t="n">
-        <v>113.4313521372826</v>
-      </c>
-      <c r="I13" t="n">
-        <v>-2.778647862717406</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H14" t="n">
-        <v>113.0422089125426</v>
-      </c>
-      <c r="I14" t="n">
-        <v>-3.167791087457388</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H15" t="n">
-        <v>119.4047800727457</v>
-      </c>
-      <c r="I15" t="n">
-        <v>3.194780072745672</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H16" t="n">
-        <v>119.4522862897727</v>
-      </c>
-      <c r="I16" t="n">
-        <v>3.242286289772679</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H17" t="n">
-        <v>112.9505369933791</v>
-      </c>
-      <c r="I17" t="n">
-        <v>-3.259463006620905</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H18" t="n">
-        <v>119.8008429433546</v>
-      </c>
-      <c r="I18" t="n">
-        <v>3.590842943354573</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H19" t="n">
-        <v>120.0848615247812</v>
-      </c>
-      <c r="I19" t="n">
-        <v>3.874861524781238</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H20" t="n">
-        <v>120.2846715342741</v>
-      </c>
-      <c r="I20" t="n">
-        <v>4.07467153427406</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H21" t="n">
-        <v>120.5407446857358</v>
-      </c>
-      <c r="I21" t="n">
-        <v>4.330744685735851</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H22" t="n">
-        <v>111.6728351373313</v>
-      </c>
-      <c r="I22" t="n">
-        <v>-4.537164862668675</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H23" t="n">
-        <v>111.5198341273205</v>
-      </c>
-      <c r="I23" t="n">
-        <v>-4.690165872679501</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H24" t="n">
-        <v>111.5091451725468</v>
-      </c>
-      <c r="I24" t="n">
-        <v>-4.700854827453185</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="B25" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H25" t="n">
-        <v>110.9115909574931</v>
-      </c>
-      <c r="I25" t="n">
-        <v>-5.298409042506918</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="B26" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H26" t="n">
-        <v>110.5095333493417</v>
-      </c>
-      <c r="I26" t="n">
-        <v>-5.700466650658313</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B27" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H27" t="n">
-        <v>122.0060738736179</v>
-      </c>
-      <c r="I27" t="n">
-        <v>5.796073873617928</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B28" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H28" t="n">
-        <v>122.3633824517811</v>
-      </c>
-      <c r="I28" t="n">
-        <v>6.153382451781141</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="B29" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H29" t="n">
-        <v>122.5013665982118</v>
-      </c>
-      <c r="I29" t="n">
-        <v>6.291366598211766</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="B30" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H30" t="n">
-        <v>109.8219161789881</v>
-      </c>
-      <c r="I30" t="n">
-        <v>-6.388083821011904</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="B31" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H31" t="n">
-        <v>109.4218237690051</v>
-      </c>
-      <c r="I31" t="n">
-        <v>-6.788176230994935</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="B32" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H32" t="n">
-        <v>123.0767646219372</v>
-      </c>
-      <c r="I32" t="n">
-        <v>6.86676462193725</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G33" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H33" t="n">
-        <v>109.2980257669981</v>
-      </c>
-      <c r="I33" t="n">
-        <v>-6.911974233001899</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="B34" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H34" t="n">
-        <v>108.9746655438117</v>
-      </c>
-      <c r="I34" t="n">
-        <v>-7.235334456188312</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="B35" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G35" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H35" t="n">
-        <v>123.5206879232791</v>
-      </c>
-      <c r="I35" t="n">
-        <v>7.310687923279062</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="B36" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G36" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H36" t="n">
-        <v>108.312630069708</v>
-      </c>
-      <c r="I36" t="n">
-        <v>-7.897369930292001</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G37" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H37" t="n">
-        <v>108.1252404671735</v>
-      </c>
-      <c r="I37" t="n">
-        <v>-8.084759532826482</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B38" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G38" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H38" t="n">
-        <v>124.52941655116</v>
-      </c>
-      <c r="I38" t="n">
-        <v>8.319416551160003</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="B39" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C39" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G39" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H39" t="n">
-        <v>107.8874231791001</v>
-      </c>
-      <c r="I39" t="n">
-        <v>-8.32257682089994</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C40" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G40" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H40" t="n">
-        <v>124.843615633446</v>
-      </c>
-      <c r="I40" t="n">
-        <v>8.633615633445984</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="B41" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C41" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G41" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H41" t="n">
-        <v>107.514541625082</v>
-      </c>
-      <c r="I41" t="n">
-        <v>-8.695458374918033</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="B42" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="C42" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G42" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H42" t="n">
-        <v>125.1722406267402</v>
-      </c>
-      <c r="I42" t="n">
-        <v>8.962240626740225</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="B43" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C43" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G43" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H43" t="n">
-        <v>107.1097195131203</v>
-      </c>
-      <c r="I43" t="n">
-        <v>-9.100280486879711</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B44" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C44" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G44" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H44" t="n">
-        <v>125.6918101281961</v>
-      </c>
-      <c r="I44" t="n">
-        <v>9.481810128196059</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="B45" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C45" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G45" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H45" t="n">
-        <v>106.3249556738489</v>
-      </c>
-      <c r="I45" t="n">
-        <v>-9.885044326151046</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="B46" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G46" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H46" t="n">
-        <v>126.3888768580618</v>
-      </c>
-      <c r="I46" t="n">
-        <v>10.17887685806183</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="B47" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C47" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D47" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G47" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H47" t="n">
-        <v>105.9144593201816</v>
-      </c>
-      <c r="I47" t="n">
-        <v>-10.29554067981842</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="B48" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C48" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G48" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H48" t="n">
-        <v>105.7731101023696</v>
-      </c>
-      <c r="I48" t="n">
-        <v>-10.43688989763044</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="B49" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="C49" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G49" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H49" t="n">
-        <v>105.6219642568755</v>
-      </c>
-      <c r="I49" t="n">
-        <v>-10.58803574312448</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="B50" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C50" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H50" t="n">
-        <v>126.8731240655152</v>
-      </c>
-      <c r="I50" t="n">
-        <v>10.66312406551519</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B51" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C51" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G51" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H51" t="n">
-        <v>127.2545382241535</v>
-      </c>
-      <c r="I51" t="n">
-        <v>11.0445382241535</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="B52" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="C52" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G52" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H52" t="n">
-        <v>105.1436154463029</v>
-      </c>
-      <c r="I52" t="n">
-        <v>-11.06638455369708</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="B53" t="n">
-        <v>0</v>
-      </c>
-      <c r="C53" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G53" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H53" t="n">
-        <v>104.5179789503407</v>
-      </c>
-      <c r="I53" t="n">
-        <v>-11.69202104965925</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B54" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="C54" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G54" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H54" t="n">
-        <v>128.0149858356067</v>
-      </c>
-      <c r="I54" t="n">
-        <v>11.80498583560673</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="B55" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C55" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G55" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H55" t="n">
-        <v>128.1398784362163</v>
-      </c>
-      <c r="I55" t="n">
-        <v>11.9298784362163</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="B56" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="C56" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G56" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H56" t="n">
-        <v>104.2052424471025</v>
-      </c>
-      <c r="I56" t="n">
-        <v>-12.00475755289746</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="B57" t="n">
-        <v>0</v>
-      </c>
-      <c r="C57" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="D57" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G57" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H57" t="n">
-        <v>104.1767978732165</v>
-      </c>
-      <c r="I57" t="n">
-        <v>-12.03320212678348</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="B58" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C58" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="D58" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G58" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H58" t="n">
-        <v>103.5830512268734</v>
-      </c>
-      <c r="I58" t="n">
-        <v>-12.62694877312656</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="B59" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C59" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G59" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H59" t="n">
-        <v>103.3562481128326</v>
-      </c>
-      <c r="I59" t="n">
-        <v>-12.85375188716739</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="B60" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C60" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D60" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G60" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H60" t="n">
-        <v>129.5997284124679</v>
-      </c>
-      <c r="I60" t="n">
-        <v>13.38972841246787</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B61" t="n">
-        <v>0</v>
-      </c>
-      <c r="C61" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G61" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H61" t="n">
-        <v>129.6065468125473</v>
-      </c>
-      <c r="I61" t="n">
-        <v>13.39654681254727</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="B62" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C62" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G62" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H62" t="n">
-        <v>102.6996048989201</v>
-      </c>
-      <c r="I62" t="n">
-        <v>-13.51039510107992</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="B63" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C63" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D63" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G63" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H63" t="n">
-        <v>102.6384603134468</v>
-      </c>
-      <c r="I63" t="n">
-        <v>-13.57153968655324</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B64" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C64" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="D64" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G64" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H64" t="n">
-        <v>130.2824511941463</v>
-      </c>
-      <c r="I64" t="n">
-        <v>14.07245119414627</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="B65" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C65" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="D65" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F65" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G65" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H65" t="n">
-        <v>102.0308017948742</v>
-      </c>
-      <c r="I65" t="n">
-        <v>-14.17919820512584</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="B66" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="C66" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="D66" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F66" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G66" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H66" t="n">
-        <v>130.6725516933828</v>
-      </c>
-      <c r="I66" t="n">
-        <v>14.46255169338276</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="B67" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C67" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="D67" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G67" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H67" t="n">
-        <v>101.7383203902049</v>
-      </c>
-      <c r="I67" t="n">
-        <v>-14.47167960979509</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="B68" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C68" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D68" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F68" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G68" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H68" t="n">
-        <v>101.724304025751</v>
-      </c>
-      <c r="I68" t="n">
-        <v>-14.485695974249</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="B69" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C69" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D69" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F69" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G69" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H69" t="n">
-        <v>101.1970207504834</v>
-      </c>
-      <c r="I69" t="n">
-        <v>-15.01297924951656</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="B70" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="C70" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D70" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G70" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H70" t="n">
-        <v>100.8654071236008</v>
-      </c>
-      <c r="I70" t="n">
-        <v>-15.34459287639922</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B71" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C71" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D71" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F71" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G71" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H71" t="n">
-        <v>131.5827773130376</v>
-      </c>
-      <c r="I71" t="n">
-        <v>15.37277731303756</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="B72" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="C72" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G72" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H72" t="n">
-        <v>100.4226902519484</v>
-      </c>
-      <c r="I72" t="n">
-        <v>-15.78730974805157</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="B73" t="n">
-        <v>0</v>
-      </c>
-      <c r="C73" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D73" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G73" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H73" t="n">
-        <v>100.2283552792595</v>
-      </c>
-      <c r="I73" t="n">
-        <v>-15.98164472074048</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="B74" t="n">
-        <v>0</v>
-      </c>
-      <c r="C74" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D74" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G74" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H74" t="n">
-        <v>132.2370090303878</v>
-      </c>
-      <c r="I74" t="n">
-        <v>16.02700903038782</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="B75" t="n">
-        <v>0</v>
-      </c>
-      <c r="C75" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="D75" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F75" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G75" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H75" t="n">
-        <v>100.0612923568699</v>
-      </c>
-      <c r="I75" t="n">
-        <v>-16.14870764313014</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B76" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C76" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D76" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F76" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G76" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H76" t="n">
-        <v>132.503002574689</v>
-      </c>
-      <c r="I76" t="n">
-        <v>16.29300257468903</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="B77" t="n">
-        <v>0</v>
-      </c>
-      <c r="C77" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D77" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F77" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G77" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H77" t="n">
-        <v>99.86646115390191</v>
-      </c>
-      <c r="I77" t="n">
-        <v>-16.34353884609808</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="B78" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C78" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D78" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F78" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G78" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H78" t="n">
-        <v>133.2119364111746</v>
-      </c>
-      <c r="I78" t="n">
-        <v>17.00193641117464</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="B79" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C79" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D79" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F79" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G79" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H79" t="n">
-        <v>99.19795460058323</v>
-      </c>
-      <c r="I79" t="n">
-        <v>-17.01204539941676</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="B80" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C80" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="D80" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F80" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G80" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H80" t="n">
-        <v>98.94858800426653</v>
-      </c>
-      <c r="I80" t="n">
-        <v>-17.26141199573347</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B81" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="C81" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="D81" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F81" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G81" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H81" t="n">
-        <v>133.6665892194323</v>
-      </c>
-      <c r="I81" t="n">
-        <v>17.4565892194323</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="B82" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C82" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="D82" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F82" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G82" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H82" t="n">
-        <v>98.28949028471988</v>
-      </c>
-      <c r="I82" t="n">
-        <v>-17.92050971528012</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="B83" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C83" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D83" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F83" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G83" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H83" t="n">
-        <v>98.14714426956671</v>
-      </c>
-      <c r="I83" t="n">
-        <v>-18.06285573043328</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="B84" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C84" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D84" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F84" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G84" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H84" t="n">
-        <v>97.67549794913243</v>
-      </c>
-      <c r="I84" t="n">
-        <v>-18.53450205086756</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="B85" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C85" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="D85" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F85" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G85" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H85" t="n">
-        <v>97.59241393639917</v>
-      </c>
-      <c r="I85" t="n">
-        <v>-18.61758606360083</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="B86" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C86" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="D86" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F86" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G86" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H86" t="n">
-        <v>135.01475469666</v>
-      </c>
-      <c r="I86" t="n">
-        <v>18.80475469666003</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="B87" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C87" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D87" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F87" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G87" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H87" t="n">
-        <v>135.6787689016566</v>
-      </c>
-      <c r="I87" t="n">
-        <v>19.46876890165662</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B88" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C88" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D88" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F88" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G88" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H88" t="n">
-        <v>135.7212867548465</v>
-      </c>
-      <c r="I88" t="n">
-        <v>19.51128675484652</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="B89" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="C89" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D89" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F89" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G89" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H89" t="n">
-        <v>96.64013805679431</v>
-      </c>
-      <c r="I89" t="n">
-        <v>-19.56986194320568</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="B90" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="C90" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="D90" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F90" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G90" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H90" t="n">
-        <v>96.58719880089865</v>
-      </c>
-      <c r="I90" t="n">
-        <v>-19.62280119910135</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="B91" t="n">
-        <v>0</v>
-      </c>
-      <c r="C91" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="D91" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F91" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G91" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H91" t="n">
-        <v>96.34056095067547</v>
-      </c>
-      <c r="I91" t="n">
-        <v>-19.86943904932453</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="B92" t="n">
-        <v>0</v>
-      </c>
-      <c r="C92" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D92" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F92" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G92" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H92" t="n">
-        <v>96.27991268530255</v>
-      </c>
-      <c r="I92" t="n">
-        <v>-19.93008731469745</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="B93" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C93" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D93" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F93" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G93" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H93" t="n">
-        <v>95.25871569508628</v>
-      </c>
-      <c r="I93" t="n">
-        <v>-20.95128430491371</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="B94" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="C94" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D94" t="n">
-        <v>0</v>
-      </c>
-      <c r="E94" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F94" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G94" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H94" t="n">
-        <v>137.3057721430423</v>
-      </c>
-      <c r="I94" t="n">
-        <v>21.09577214304231</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="B95" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C95" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="D95" t="n">
-        <v>0</v>
-      </c>
-      <c r="E95" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F95" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G95" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H95" t="n">
-        <v>95.0396610883339</v>
-      </c>
-      <c r="I95" t="n">
-        <v>-21.17033891166609</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B96" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C96" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="D96" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F96" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G96" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H96" t="n">
-        <v>137.4737444978791</v>
-      </c>
-      <c r="I96" t="n">
-        <v>21.26374449787907</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="B97" t="n">
-        <v>0</v>
-      </c>
-      <c r="C97" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="D97" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F97" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G97" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H97" t="n">
-        <v>138.0851412027138</v>
-      </c>
-      <c r="I97" t="n">
-        <v>21.87514120271381</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="B98" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C98" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D98" t="n">
-        <v>0</v>
-      </c>
-      <c r="E98" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F98" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G98" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H98" t="n">
-        <v>94.26348674425928</v>
-      </c>
-      <c r="I98" t="n">
-        <v>-21.94651325574071</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="B99" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C99" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D99" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F99" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G99" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H99" t="n">
-        <v>93.98780712231489</v>
-      </c>
-      <c r="I99" t="n">
-        <v>-22.2221928776851</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="B100" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C100" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="D100" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F100" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G100" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H100" t="n">
-        <v>93.62669187251389</v>
-      </c>
-      <c r="I100" t="n">
-        <v>-22.58330812748611</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B101" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="C101" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D101" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F101" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G101" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H101" t="n">
-        <v>139.3181926032578</v>
-      </c>
-      <c r="I101" t="n">
-        <v>23.10819260325782</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="B102" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C102" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D102" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F102" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G102" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H102" t="n">
-        <v>139.5507487568341</v>
-      </c>
-      <c r="I102" t="n">
-        <v>23.34074875683409</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="B103" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="C103" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D103" t="n">
-        <v>0</v>
-      </c>
-      <c r="E103" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F103" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G103" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H103" t="n">
-        <v>92.8575858616402</v>
-      </c>
-      <c r="I103" t="n">
-        <v>-23.35241413835979</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="B104" t="n">
-        <v>0</v>
-      </c>
-      <c r="C104" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F104" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G104" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H104" t="n">
-        <v>92.814660747449</v>
-      </c>
-      <c r="I104" t="n">
-        <v>-23.395339252551</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="B105" t="n">
-        <v>0</v>
-      </c>
-      <c r="C105" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="D105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E105" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F105" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G105" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H105" t="n">
-        <v>92.33147009134557</v>
-      </c>
-      <c r="I105" t="n">
-        <v>-23.87852990865443</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="B106" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C106" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D106" t="n">
-        <v>0</v>
-      </c>
-      <c r="E106" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F106" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G106" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H106" t="n">
-        <v>91.56884338590604</v>
-      </c>
-      <c r="I106" t="n">
-        <v>-24.64115661409396</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="B107" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C107" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="D107" t="n">
-        <v>0</v>
-      </c>
-      <c r="E107" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F107" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G107" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H107" t="n">
-        <v>141.7578093908455</v>
-      </c>
-      <c r="I107" t="n">
-        <v>25.54780939084547</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="B108" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C108" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E108" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F108" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G108" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H108" t="n">
-        <v>141.9844415508911</v>
-      </c>
-      <c r="I108" t="n">
-        <v>25.7744415508911</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="B109" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C109" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D109" t="n">
-        <v>0</v>
-      </c>
-      <c r="E109" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F109" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G109" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H109" t="n">
-        <v>90.38320030823063</v>
-      </c>
-      <c r="I109" t="n">
-        <v>-25.82679969176937</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="B110" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C110" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="D110" t="n">
-        <v>0</v>
-      </c>
-      <c r="E110" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F110" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G110" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H110" t="n">
-        <v>90.37982921895185</v>
-      </c>
-      <c r="I110" t="n">
-        <v>-25.83017078104814</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="B111" t="n">
-        <v>0</v>
-      </c>
-      <c r="C111" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D111" t="n">
-        <v>0</v>
-      </c>
-      <c r="E111" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F111" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G111" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H111" t="n">
-        <v>89.28876054422253</v>
-      </c>
-      <c r="I111" t="n">
-        <v>-26.92123945577747</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="B112" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="C112" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="D112" t="n">
-        <v>0</v>
-      </c>
-      <c r="E112" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F112" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G112" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H112" t="n">
-        <v>89.07503366648609</v>
-      </c>
-      <c r="I112" t="n">
-        <v>-27.1349663335139</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B113" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C113" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D113" t="n">
-        <v>0</v>
-      </c>
-      <c r="E113" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F113" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G113" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H113" t="n">
-        <v>143.3647116827206</v>
-      </c>
-      <c r="I113" t="n">
-        <v>27.15471168272056</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="B114" t="n">
-        <v>0</v>
-      </c>
-      <c r="C114" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D114" t="n">
-        <v>0</v>
-      </c>
-      <c r="E114" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F114" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G114" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H114" t="n">
-        <v>143.9332733750397</v>
-      </c>
-      <c r="I114" t="n">
-        <v>27.72327337503974</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="B115" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="C115" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D115" t="n">
-        <v>0</v>
-      </c>
-      <c r="E115" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F115" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G115" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H115" t="n">
-        <v>143.9389925927019</v>
-      </c>
-      <c r="I115" t="n">
-        <v>27.72899259270186</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="B116" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C116" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="D116" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F116" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G116" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H116" t="n">
-        <v>87.87897107672582</v>
-      </c>
-      <c r="I116" t="n">
-        <v>-28.33102892327418</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="B117" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C117" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="D117" t="n">
-        <v>0</v>
-      </c>
-      <c r="E117" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F117" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G117" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H117" t="n">
-        <v>86.77859349414634</v>
-      </c>
-      <c r="I117" t="n">
-        <v>-29.43140650585366</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="B118" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C118" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="D118" t="n">
-        <v>0</v>
-      </c>
-      <c r="E118" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F118" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G118" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H118" t="n">
-        <v>145.8895611024936</v>
-      </c>
-      <c r="I118" t="n">
-        <v>29.67956110249357</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="B119" t="n">
-        <v>0</v>
-      </c>
-      <c r="C119" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="D119" t="n">
-        <v>0</v>
-      </c>
-      <c r="E119" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F119" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G119" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H119" t="n">
-        <v>85.76286034099607</v>
-      </c>
-      <c r="I119" t="n">
-        <v>-30.44713965900392</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="B120" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C120" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D120" t="n">
-        <v>0</v>
-      </c>
-      <c r="E120" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F120" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G120" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H120" t="n">
-        <v>147.8368498800342</v>
-      </c>
-      <c r="I120" t="n">
-        <v>31.62684988003424</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="B121" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C121" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D121" t="n">
-        <v>0</v>
-      </c>
-      <c r="E121" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F121" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G121" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H121" t="n">
-        <v>148.9541284051222</v>
-      </c>
-      <c r="I121" t="n">
-        <v>32.74412840512217</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="B122" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="C122" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="D122" t="n">
-        <v>0</v>
-      </c>
-      <c r="E122" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F122" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G122" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H122" t="n">
-        <v>150.5722130423615</v>
-      </c>
-      <c r="I122" t="n">
-        <v>34.36221304236146</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="B123" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C123" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D123" t="n">
-        <v>0</v>
-      </c>
-      <c r="E123" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F123" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G123" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H123" t="n">
-        <v>152.228373448153</v>
-      </c>
-      <c r="I123" t="n">
-        <v>36.01837344815301</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="B124" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C124" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="D124" t="n">
-        <v>0</v>
-      </c>
-      <c r="E124" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F124" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G124" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H124" t="n">
-        <v>155.9238152593533</v>
-      </c>
-      <c r="I124" t="n">
-        <v>39.71381525935327</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="B125" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="C125" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D125" t="n">
-        <v>0</v>
-      </c>
-      <c r="E125" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F125" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G125" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H125" t="n">
-        <v>157.2054334920209</v>
-      </c>
-      <c r="I125" t="n">
-        <v>40.99543349202095</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="B126" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C126" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D126" t="n">
-        <v>0</v>
-      </c>
-      <c r="E126" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F126" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G126" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H126" t="n">
-        <v>162.8935021135843</v>
-      </c>
-      <c r="I126" t="n">
-        <v>46.68350211358434</v>
       </c>
     </row>
   </sheetData>
